--- a/Result/profitability/2465.xlsx
+++ b/Result/profitability/2465.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.17125</v>
+        <v>0.17375</v>
       </c>
       <c r="N2" t="n">
-        <v>10.28625</v>
+        <v>10.9475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.15125</v>
+        <v>0.2475</v>
       </c>
       <c r="N3" t="n">
-        <v>9.915000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0275</v>
+        <v>0.1475</v>
       </c>
       <c r="N4" t="n">
-        <v>9.50625</v>
+        <v>8.41375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09375</v>
+        <v>0.07749999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.775</v>
+        <v>9.06875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1975</v>
+        <v>0.06124999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>8.393750000000001</v>
+        <v>9.33375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.21375</v>
+        <v>-0.05125000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>9.303750000000001</v>
+        <v>9.535</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3387500000000001</v>
+        <v>-0.2775</v>
       </c>
       <c r="N8" t="n">
-        <v>9.6175</v>
+        <v>9.8225</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.25</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5599999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>9.58</v>
@@ -1772,7 +1772,7 @@
         <v>0.29</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4037500000000001</v>
+        <v>-0.40375</v>
       </c>
       <c r="N11" t="n">
         <v>10.49875</v>
@@ -1899,7 +1899,7 @@
         <v>0.61</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2575000000000001</v>
+        <v>-0.2575</v>
       </c>
       <c r="N12" t="n">
         <v>11.7325</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2506</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2198</v>
+      </c>
+      <c r="E75" t="n">
+        <v>308</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>173</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.91%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>175</v>
+      </c>
+      <c r="K75" t="n">
+        <v>154</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.06749999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.57625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4260869565217391</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.639999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1539906103286384</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.074074074074074</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2364185110663983</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
